--- a/Idée amélioration appli.xlsx
+++ b/Idée amélioration appli.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francois\source\repos\LoGeCui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9259603A-2724-464C-9561-545E5184BBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCC8503-9231-4089-967B-B15E007444C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Rechercher les prix des produits dans plusieurs magasins</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>Demain</t>
+  </si>
+  <si>
+    <t>Gestion de menu équilibrés avec options végétarien, vegan , allergie .</t>
   </si>
 </sst>
 </file>
@@ -413,6 +416,11 @@
         <v>3</v>
       </c>
     </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
     </row>
